--- a/treescan/qa/crossval_treescan.xlsx
+++ b/treescan/qa/crossval_treescan.xlsx
@@ -21,7 +21,7 @@
     <t>Validated against hand-computed values and R TreeMineR</t>
   </si>
   <si>
-    <t>Date:  1 Mar 2026</t>
+    <t>Date:  7 Mar 2026</t>
   </si>
   <si>
     <t>Test</t>
